--- a/Team-Data/2008-09/1-23-2008-09.xlsx
+++ b/Team-Data/2008-09/1-23-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,106 +728,106 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.619</v>
+        <v>0.61</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="L2" t="n">
         <v>8.1</v>
       </c>
       <c r="M2" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O2" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P2" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0.742</v>
       </c>
       <c r="R2" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U2" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="V2" t="n">
         <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
         <v>20.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.7</v>
+        <v>98.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ2" t="n">
         <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -772,31 +839,31 @@
         <v>12</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS2" t="n">
         <v>21</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
         <v>18</v>
@@ -808,10 +875,10 @@
         <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.795</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.381</v>
+        <v>0.378</v>
       </c>
       <c r="O3" t="n">
         <v>20.6</v>
       </c>
       <c r="P3" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="V3" t="n">
         <v>16.1</v>
@@ -903,25 +970,25 @@
         <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>100.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -930,13 +997,13 @@
         <v>3</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
         <v>13</v>
       </c>
       <c r="AI3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -945,19 +1012,19 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM3" t="n">
         <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
         <v>5</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
         <v>12</v>
@@ -966,10 +1033,10 @@
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -981,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
         <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.419</v>
+        <v>0.405</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="J4" t="n">
         <v>75.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
         <v>5.3</v>
@@ -1055,64 +1122,64 @@
         <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>0.356</v>
+        <v>0.353</v>
       </c>
       <c r="O4" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R4" t="n">
         <v>10.7</v>
       </c>
       <c r="S4" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T4" t="n">
         <v>39.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V4" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
         <v>4.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA4" t="n">
         <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>91.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.7</v>
+        <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
         <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1133,16 +1200,16 @@
         <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR4" t="n">
         <v>18</v>
@@ -1154,16 +1221,16 @@
         <v>27</v>
       </c>
       <c r="AU4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW4" t="n">
         <v>19</v>
       </c>
-      <c r="AV4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>15</v>
-      </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -1210,13 +1277,13 @@
         <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>0.395</v>
+        <v>0.419</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1228,79 +1295,79 @@
         <v>84</v>
       </c>
       <c r="K5" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L5" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N5" t="n">
         <v>0.374</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="R5" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V5" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
         <v>4</v>
@@ -1312,16 +1379,16 @@
         <v>19</v>
       </c>
       <c r="AM5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="n">
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1339,28 +1406,28 @@
         <v>13</v>
       </c>
       <c r="AV5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>21</v>
       </c>
-      <c r="AW5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>24</v>
-      </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -1392,34 +1459,34 @@
         <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.825</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L6" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="M6" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.371</v>
+        <v>0.365</v>
       </c>
       <c r="O6" t="n">
         <v>18.9</v>
@@ -1428,115 +1495,115 @@
         <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
       <c r="U6" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="W6" t="n">
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Z6" t="n">
         <v>20.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>100.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR6" t="n">
         <v>21</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -1571,70 +1638,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>0.581</v>
+        <v>0.571</v>
       </c>
       <c r="H7" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J7" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.453</v>
+        <v>0.451</v>
       </c>
       <c r="L7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.338</v>
+        <v>0.336</v>
       </c>
       <c r="O7" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P7" t="n">
         <v>21.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>11.6</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T7" t="n">
-        <v>43.5</v>
+        <v>43.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V7" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z7" t="n">
         <v>18.8</v>
@@ -1643,22 +1710,22 @@
         <v>19.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>16</v>
@@ -1670,16 +1737,16 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
         <v>12</v>
       </c>
       <c r="AM7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
         <v>25</v>
@@ -1691,22 +1758,22 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
         <v>3</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
         <v>8</v>
@@ -1724,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
         <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
@@ -1855,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
         <v>24</v>
@@ -1879,7 +1946,7 @@
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU8" t="n">
         <v>4</v>
@@ -1891,19 +1958,19 @@
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -1935,70 +2002,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.571</v>
+        <v>0.585</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J9" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="K9" t="n">
         <v>0.453</v>
       </c>
       <c r="L9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M9" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="N9" t="n">
         <v>0.337</v>
       </c>
       <c r="O9" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="P9" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.747</v>
+        <v>0.74</v>
       </c>
       <c r="R9" t="n">
         <v>10.7</v>
       </c>
       <c r="S9" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T9" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="U9" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V9" t="n">
         <v>12.2</v>
       </c>
       <c r="W9" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X9" t="n">
         <v>5.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z9" t="n">
         <v>21.1</v>
@@ -2010,31 +2077,31 @@
         <v>93.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG9" t="n">
         <v>11</v>
       </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2043,49 +2110,49 @@
         <v>26</v>
       </c>
       <c r="AN9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP9" t="n">
         <v>26</v>
       </c>
-      <c r="AO9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>25</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR9" t="n">
         <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AV9" t="n">
         <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="n">
         <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>0.295</v>
+        <v>0.302</v>
       </c>
       <c r="H10" t="n">
         <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J10" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L10" t="n">
         <v>6.5</v>
@@ -2147,58 +2214,58 @@
         <v>18.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O10" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="P10" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="R10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S10" t="n">
         <v>29.9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="R10" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>30</v>
       </c>
       <c r="T10" t="n">
         <v>42.4</v>
       </c>
       <c r="U10" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X10" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y10" t="n">
         <v>5.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA10" t="n">
         <v>24.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>107.3</v>
+        <v>107.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.8</v>
+        <v>-4.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>25</v>
@@ -2210,13 +2277,13 @@
         <v>6</v>
       </c>
       <c r="AI10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>16</v>
@@ -2237,25 +2304,25 @@
         <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
         <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" t="n">
         <v>27</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.614</v>
+        <v>0.628</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,7 +2384,7 @@
         <v>35.3</v>
       </c>
       <c r="J11" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K11" t="n">
         <v>0.445</v>
@@ -2326,37 +2393,37 @@
         <v>7.3</v>
       </c>
       <c r="M11" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.369</v>
+        <v>0.371</v>
       </c>
       <c r="O11" t="n">
         <v>19.6</v>
       </c>
       <c r="P11" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
       </c>
       <c r="S11" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T11" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U11" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V11" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W11" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
         <v>3.7</v>
@@ -2365,28 +2432,28 @@
         <v>5.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -2395,10 +2462,10 @@
         <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
         <v>10</v>
@@ -2407,7 +2474,7 @@
         <v>9</v>
       </c>
       <c r="AN11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
         <v>9</v>
@@ -2416,7 +2483,7 @@
         <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2425,34 +2492,34 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>19</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -2481,49 +2548,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
         <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>0.372</v>
+        <v>0.357</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>86.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L12" t="n">
         <v>7.4</v>
       </c>
       <c r="M12" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="P12" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S12" t="n">
         <v>32.5</v>
@@ -2553,13 +2620,13 @@
         <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.3</v>
+        <v>-2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>23</v>
@@ -2574,31 +2641,31 @@
         <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ12" t="n">
         <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM12" t="n">
         <v>8</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
         <v>13</v>
@@ -2613,16 +2680,16 @@
         <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2631,7 +2698,7 @@
         <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>0.238</v>
+        <v>0.22</v>
       </c>
       <c r="H13" t="n">
         <v>48.7</v>
@@ -2684,79 +2751,79 @@
         <v>82.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="L13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M13" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.324</v>
+        <v>0.316</v>
       </c>
       <c r="O13" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P13" t="n">
         <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.751</v>
+        <v>0.749</v>
       </c>
       <c r="R13" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S13" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="T13" t="n">
-        <v>41.6</v>
+        <v>41.9</v>
       </c>
       <c r="U13" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V13" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y13" t="n">
         <v>5.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.9</v>
+        <v>-7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF13" t="n">
         <v>27</v>
       </c>
       <c r="AG13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH13" t="n">
         <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2771,7 +2838,7 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO13" t="n">
         <v>26</v>
@@ -2780,16 +2847,16 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR13" t="n">
         <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
         <v>27</v>
@@ -2801,19 +2868,19 @@
         <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY13" t="n">
         <v>28</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>25</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.805</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
@@ -2863,7 +2930,7 @@
         <v>40</v>
       </c>
       <c r="J14" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K14" t="n">
         <v>0.477</v>
@@ -2872,31 +2939,31 @@
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.377</v>
+        <v>0.381</v>
       </c>
       <c r="O14" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P14" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
         <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.4</v>
+        <v>31.6</v>
       </c>
       <c r="T14" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
         <v>13.7</v>
@@ -2905,7 +2972,7 @@
         <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
         <v>4.4</v>
@@ -2914,25 +2981,25 @@
         <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.1</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>29</v>
@@ -2941,10 +3008,10 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,13 +3029,13 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2977,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -3027,49 +3094,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" t="n">
         <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>0.262</v>
+        <v>0.268</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J15" t="n">
         <v>77</v>
       </c>
       <c r="K15" t="n">
-        <v>0.449</v>
+        <v>0.451</v>
       </c>
       <c r="L15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M15" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.322</v>
+        <v>0.319</v>
       </c>
       <c r="O15" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P15" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R15" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
         <v>28</v>
@@ -3078,16 +3145,16 @@
         <v>38.1</v>
       </c>
       <c r="U15" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="V15" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W15" t="n">
         <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y15" t="n">
         <v>5</v>
@@ -3099,13 +3166,13 @@
         <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3135,19 +3202,19 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP15" t="n">
         <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
         <v>28</v>
@@ -3165,7 +3232,7 @@
         <v>9</v>
       </c>
       <c r="AX15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3308,19 +3375,19 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>13</v>
       </c>
       <c r="AM16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
         <v>24</v>
@@ -3353,7 +3420,7 @@
         <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -3406,40 +3473,40 @@
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="J17" t="n">
         <v>81.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O17" t="n">
         <v>19.5</v>
       </c>
       <c r="P17" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0.782</v>
       </c>
       <c r="R17" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U17" t="n">
         <v>21.2</v>
@@ -3454,19 +3521,19 @@
         <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="AA17" t="n">
         <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,13 +3542,13 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>15</v>
@@ -3499,25 +3566,25 @@
         <v>23</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
         <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
@@ -3526,13 +3593,13 @@
         <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3541,10 +3608,10 @@
         <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -3573,43 +3640,43 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
         <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>0.341</v>
+        <v>0.325</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J18" t="n">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L18" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M18" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.349</v>
+        <v>0.344</v>
       </c>
       <c r="O18" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P18" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q18" t="n">
         <v>0.758</v>
@@ -3618,19 +3685,19 @@
         <v>12.6</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
         <v>42.3</v>
       </c>
       <c r="U18" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V18" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W18" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X18" t="n">
         <v>4.2</v>
@@ -3639,19 +3706,19 @@
         <v>6.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.3</v>
+        <v>-3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
@@ -3666,10 +3733,10 @@
         <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3678,7 +3745,7 @@
         <v>21</v>
       </c>
       <c r="AM18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="n">
         <v>22</v>
@@ -3687,16 +3754,16 @@
         <v>17</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT18" t="n">
         <v>11</v>
@@ -3705,10 +3772,10 @@
         <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX18" t="n">
         <v>25</v>
@@ -3717,16 +3784,16 @@
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -3755,85 +3822,85 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" t="n">
         <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>0.442</v>
+        <v>0.452</v>
       </c>
       <c r="H19" t="n">
         <v>48.7</v>
       </c>
       <c r="I19" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J19" t="n">
         <v>80.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L19" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N19" t="n">
         <v>0.378</v>
       </c>
       <c r="O19" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R19" t="n">
         <v>11.2</v>
       </c>
       <c r="S19" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T19" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U19" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="V19" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="W19" t="n">
         <v>6.8</v>
       </c>
       <c r="X19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="AC19" t="n">
         <v>-3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3848,7 +3915,7 @@
         <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
         <v>15</v>
@@ -3860,10 +3927,10 @@
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
         <v>8</v>
@@ -3878,7 +3945,7 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT19" t="n">
         <v>21</v>
@@ -3887,16 +3954,16 @@
         <v>29</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY19" t="n">
         <v>20</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>21</v>
       </c>
       <c r="AZ19" t="n">
         <v>27</v>
@@ -3905,10 +3972,10 @@
         <v>14</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -3937,64 +4004,64 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" t="n">
         <v>26</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>0.65</v>
+        <v>0.667</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="J20" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.392</v>
+        <v>0.386</v>
       </c>
       <c r="O20" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P20" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S20" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="T20" t="n">
-        <v>38.6</v>
+        <v>38.9</v>
       </c>
       <c r="U20" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V20" t="n">
         <v>12.6</v>
       </c>
       <c r="W20" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
@@ -4003,28 +4070,28 @@
         <v>3.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
       </c>
       <c r="AF20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG20" t="n">
         <v>6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>7</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
@@ -4039,19 +4106,19 @@
         <v>9</v>
       </c>
       <c r="AL20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN20" t="n">
         <v>3</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4060,7 +4127,7 @@
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AT20" t="n">
         <v>29</v>
@@ -4072,25 +4139,25 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.429</v>
+        <v>0.415</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,37 +4204,37 @@
         <v>37.5</v>
       </c>
       <c r="J21" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L21" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="M21" t="n">
         <v>29</v>
       </c>
       <c r="N21" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O21" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P21" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.802</v>
+        <v>0.8</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T21" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U21" t="n">
         <v>21.4</v>
@@ -4182,40 +4249,40 @@
         <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z21" t="n">
         <v>19.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.6</v>
+        <v>-3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK21" t="n">
         <v>29</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
@@ -4236,7 +4303,7 @@
         <v>27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
@@ -4248,19 +4315,19 @@
         <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ21" t="n">
         <v>5</v>
@@ -4272,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" t="n">
         <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>0.205</v>
+        <v>0.209</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J22" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.447</v>
@@ -4328,61 +4395,61 @@
         <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.377</v>
+        <v>0.374</v>
       </c>
       <c r="O22" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="P22" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.769</v>
+        <v>0.766</v>
       </c>
       <c r="R22" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S22" t="n">
         <v>30.9</v>
       </c>
       <c r="T22" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
         <v>16.5</v>
       </c>
       <c r="W22" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X22" t="n">
         <v>4.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.7</v>
+        <v>-6.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF22" t="n">
         <v>30</v>
@@ -4391,7 +4458,7 @@
         <v>30</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>17</v>
@@ -4400,7 +4467,7 @@
         <v>11</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,19 +4476,19 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
         <v>11</v>
@@ -4430,28 +4497,28 @@
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
         <v>21</v>
       </c>
       <c r="AY22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC22" t="n">
         <v>28</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>8.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF23" t="n">
         <v>3</v>
@@ -4573,13 +4640,13 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
         <v>8</v>
@@ -4594,31 +4661,31 @@
         <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
       </c>
       <c r="AV23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW23" t="n">
         <v>14</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>11</v>
       </c>
       <c r="AX23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE24" t="n">
         <v>17</v>
@@ -4764,10 +4831,10 @@
         <v>14</v>
       </c>
       <c r="AK24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AL24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM24" t="n">
         <v>29</v>
@@ -4776,28 +4843,28 @@
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
         <v>8</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -4847,64 +4914,64 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.575</v>
       </c>
       <c r="H25" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38.4</v>
+        <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.495</v>
+        <v>0.498</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O25" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="P25" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="R25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T25" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U25" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V25" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W25" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X25" t="n">
         <v>5</v>
@@ -4916,25 +4983,25 @@
         <v>20.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.8</v>
+        <v>104.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
         <v>17</v>
@@ -4964,7 +5031,7 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>27</v>
@@ -4973,10 +5040,10 @@
         <v>8</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -4988,7 +5055,7 @@
         <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
         <v>10</v>
@@ -4997,10 +5064,10 @@
         <v>7</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.61</v>
+        <v>0.595</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="L26" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M26" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O26" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="P26" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.767</v>
+        <v>0.764</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
@@ -5077,10 +5144,10 @@
         <v>27.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
@@ -5095,58 +5162,58 @@
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF26" t="n">
         <v>10</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>8</v>
       </c>
       <c r="AG26" t="n">
         <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM26" t="n">
         <v>10</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>19</v>
       </c>
       <c r="AU26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5167,22 +5234,22 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5298,10 +5365,10 @@
         <v>28</v>
       </c>
       <c r="AG27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5313,7 +5380,7 @@
         <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM27" t="n">
         <v>16</v>
@@ -5325,10 +5392,10 @@
         <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR27" t="n">
         <v>23</v>
@@ -5340,13 +5407,13 @@
         <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F28" t="n">
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,19 +5478,19 @@
         <v>36.8</v>
       </c>
       <c r="J28" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K28" t="n">
         <v>0.464</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.395</v>
+        <v>0.397</v>
       </c>
       <c r="O28" t="n">
         <v>15.1</v>
@@ -5432,28 +5499,28 @@
         <v>19.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.761</v>
+        <v>0.756</v>
       </c>
       <c r="R28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S28" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T28" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="U28" t="n">
         <v>21.8</v>
       </c>
       <c r="V28" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y28" t="n">
         <v>4.1</v>
@@ -5462,7 +5529,7 @@
         <v>18.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB28" t="n">
         <v>96.90000000000001</v>
@@ -5471,7 +5538,7 @@
         <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5486,10 +5553,10 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5510,13 +5577,13 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>22</v>
@@ -5531,10 +5598,10 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -5575,43 +5642,43 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F29" t="n">
         <v>28</v>
       </c>
       <c r="G29" t="n">
-        <v>0.378</v>
+        <v>0.364</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J29" t="n">
         <v>78.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
         <v>6.2</v>
       </c>
       <c r="M29" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0.377</v>
+        <v>0.375</v>
       </c>
       <c r="O29" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q29" t="n">
         <v>0.823</v>
@@ -5620,19 +5687,19 @@
         <v>9</v>
       </c>
       <c r="S29" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T29" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U29" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V29" t="n">
         <v>13.5</v>
       </c>
       <c r="W29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="X29" t="n">
         <v>4.8</v>
@@ -5641,22 +5708,22 @@
         <v>4.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.3</v>
+        <v>-2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF29" t="n">
         <v>24</v>
@@ -5668,28 +5735,28 @@
         <v>18</v>
       </c>
       <c r="AI29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>22</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>23</v>
-      </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>18</v>
       </c>
       <c r="AM29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AN29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,19 +5765,19 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX29" t="n">
         <v>17</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>3</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH30" t="n">
         <v>12</v>
@@ -5877,7 +5944,7 @@
         <v>11</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5889,16 +5956,16 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ30" t="n">
         <v>25</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>-6.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF31" t="n">
         <v>28</v>
@@ -6029,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI31" t="n">
         <v>16</v>
@@ -6038,7 +6105,7 @@
         <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6047,7 +6114,7 @@
         <v>24</v>
       </c>
       <c r="AN31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO31" t="n">
         <v>29</v>
@@ -6056,7 +6123,7 @@
         <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
         <v>10</v>
@@ -6068,13 +6135,13 @@
         <v>25</v>
       </c>
       <c r="AU31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW31" t="n">
         <v>10</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>9</v>
       </c>
       <c r="AX31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-23-2008-09</t>
+          <t>2009-01-23</t>
         </is>
       </c>
     </row>
